--- a/src/features/expenses/nota-spese-template.xlsx
+++ b/src/features/expenses/nota-spese-template.xlsx
@@ -172,7 +172,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="10">
+  <numFmts count="12">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -183,6 +183,8 @@
     <numFmt numFmtId="170" formatCode="&quot;€&quot;\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="#,##0.0_)&quot;km&quot;;\(#,##0.0\)&quot;km&quot;"/>
     <numFmt numFmtId="172" formatCode="0.0000"/>
+    <numFmt numFmtId="173" formatCode="&quot;€&quot;\ #,##0.000&quot;/km&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -957,7 +959,7 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1506,6 +1508,14 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="12" fillId="3" borderId="28" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="12" fillId="3" borderId="28" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3007,8 +3017,8 @@
         <v>10</v>
       </c>
       <c r="J6" s="18"/>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138"/>
+      <c r="K6" s="145"/>
+      <c r="L6" s="145"/>
       <c r="M6" s="29"/>
       <c r="N6" s="104">
         <f>SUMIF(B15:B16,"Taxi",O15:O16)+SUMIF(B15:B16,"Carburante",O15:O16)+SUMIF(B15:B16,"Noleggio auto",O15:O16)+SUMIF(B15:B16,"Carburante auto a noleggio",O15:O16)+SUMIF(B15:B16,"Pedaggi",O15:O16)+SUMIF(B15:B16,"Parcheggio",O15:O16)</f>
@@ -3059,8 +3069,8 @@
         <v>16</v>
       </c>
       <c r="J8" s="18"/>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
+      <c r="K8" s="146"/>
+      <c r="L8" s="146"/>
       <c r="M8" s="29"/>
       <c r="N8" s="102">
         <f>SUMIF(B15:B16,"Volo",O15:O16)+SUMIF(B15:B16,"Treno",O15:O16)</f>
@@ -3087,8 +3097,8 @@
         <v>19</v>
       </c>
       <c r="J9" s="18"/>
-      <c r="K9" s="138"/>
-      <c r="L9" s="138"/>
+      <c r="K9" s="146"/>
+      <c r="L9" s="146"/>
       <c r="M9" s="29"/>
       <c r="N9" s="19" t="s">
         <v>20</v>
